--- a/test/testcases/testcase27_csv_csv_bigdata_match.xlsx
+++ b/test/testcases/testcase27_csv_csv_bigdata_match.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My_Workspaces\GitHub\QE_ATF\test\testcases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D4EB74-66B7-4405-9155-324A70769611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A047AA-46EB-4E8B-9DCA-2CBB559FC30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="testcase" sheetId="1" r:id="rId1"/>
@@ -132,9 +132,6 @@
     <t>Auto</t>
   </si>
   <si>
-    <t>/app/test/s2t/s2t_27_csv_csv_bigdata_match.xlsx</t>
-  </si>
-  <si>
     <t>testcase27_csv_csv_bigdata_match</t>
   </si>
   <si>
@@ -145,6 +142,9 @@
   </si>
   <si>
     <t>id,created_on</t>
+  </si>
+  <si>
+    <t>test/s2t/s2t_27_csv_csv_bigdata_match.xlsx</t>
   </si>
 </sst>
 </file>
@@ -551,7 +551,7 @@
         <v>11</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -629,7 +629,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -710,7 +710,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -736,7 +736,7 @@
         <v>10</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -744,7 +744,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -752,7 +752,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
